--- a/documentation/plans/master-data/evidence/barcode-import/barcode-sample.xlsx
+++ b/documentation/plans/master-data/evidence/barcode-import/barcode-sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Barcodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,108 +413,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item Code</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Barcode</t>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Barcode (EAN-13)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Barcode Image</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>DEMO-BASIN-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>9555123400042</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>DEMO-BASIN-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>9555123400059</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>DEMO-BASIN-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>9555123400035</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>DEMO-TAP-01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>DEMO-NOT-REAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>9555123400066</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>DEMO-TAP-02</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9.55512E+12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>DEMO-TAP-03</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>9555123400011</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9555123400073</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>DEMO-SINK-01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9555123400073</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Same barcode as DEMO-TAP-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEMO-SINK-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
